--- a/output/pdf_financials_xlsx/STRR.xlsx
+++ b/output/pdf_financials_xlsx/STRR.xlsx
@@ -649,22 +649,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.040098</v>
+        <v>0.5332480000000001</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.4502</v>
+        <v>2.894725</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.494271</v>
+        <v>3.087941</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.184625</v>
+        <v>2.841305</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.258213</v>
+        <v>5.05779</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.167883</v>
+        <v>10.409724</v>
       </c>
     </row>
     <row r="11">
@@ -674,22 +674,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.035755</v>
+        <v>-0.528905</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.08737499999999999</v>
+        <v>-2.5319</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.219481</v>
+        <v>-2.374189</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.316729</v>
+        <v>-2.339951</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.15465</v>
+        <v>-4.644927</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.01026</v>
+        <v>-10.231581</v>
       </c>
     </row>
     <row r="12">
@@ -699,22 +699,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.003499</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.048401</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.0339</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.07888000000000001</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.071738</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.025115</v>
       </c>
     </row>
     <row r="13">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.799893</v>
+        <v>-0.803392</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.372873</v>
+        <v>-2.421274</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>17.724727</v>
+        <v>17.690827</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>5.873192</v>
+        <v>5.794312</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-23.858579</v>
+        <v>-23.930317</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-9.141473</v>
+        <v>-9.166588000000001</v>
       </c>
     </row>
     <row r="28">
@@ -1152,22 +1152,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.799893</v>
+        <v>-0.803392</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.372873</v>
+        <v>-2.421274</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>17.724727</v>
+        <v>17.690827</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>5.873192</v>
+        <v>5.794312</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-23.858579</v>
+        <v>-23.930317</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-9.141473</v>
+        <v>-9.166588000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1292,13 +1292,13 @@
         <v>2.478184</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>2.880019</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.37763</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.802136</v>
       </c>
     </row>
     <row r="35">
@@ -1342,13 +1342,13 @@
         <v>2.478184</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.78409</v>
+        <v>3.664109</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.823674</v>
+        <v>2.201304</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>2.839399</v>
+        <v>3.641535</v>
       </c>
     </row>
     <row r="37">
@@ -1642,13 +1642,13 @@
         <v>0.043621</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.915824</v>
+        <v>0.035805</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.41099</v>
+        <v>0.03336</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.838286</v>
+        <v>0.03615</v>
       </c>
     </row>
     <row r="49">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -13042,26 +13042,26 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E204" s="5" t="n">
-        <v>-0.5332480000000001</v>
+        <v>0.5332480000000001</v>
       </c>
       <c r="F204" s="5" t="n">
-        <v>-2.894725</v>
+        <v>2.894725</v>
       </c>
       <c r="G204" s="5" t="n">
-        <v>-3.087941</v>
+        <v>3.087941</v>
       </c>
       <c r="H204" s="5" t="n">
-        <v>-2.841305</v>
+        <v>2.841305</v>
       </c>
       <c r="I204" s="5" t="n">
-        <v>-5.05779</v>
+        <v>5.05779</v>
       </c>
       <c r="J204" s="5" t="n">
-        <v>-10.409724</v>
+        <v>10.409724</v>
       </c>
     </row>
     <row r="205">
@@ -13126,7 +13126,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -14926,7 +14926,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E246" s="5" t="n">

--- a/output/pdf_financials_xlsx/STRR.xlsx
+++ b/output/pdf_financials_xlsx/STRR.xlsx
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.695365</v>
       </c>
     </row>
     <row r="116">
@@ -3492,7 +3492,7 @@
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>0</v>
+        <v>-0.292383</v>
       </c>
       <c r="C121" s="3" t="n">
         <v>0</v>
@@ -6938,7 +6938,11 @@
           <t>Proceeds from sale of marketable securities (Note 6)</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -9582,7 +9586,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -11386,7 +11394,11 @@
           <t>Repurchase of shares</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E167" s="5" t="n">
         <v>-0.292383</v>
       </c>
